--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -6644,7 +6644,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -6644,7 +6644,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -6644,7 +6644,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -6644,7 +6644,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -6644,7 +6644,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -6644,7 +6644,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -8690,7 +8690,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -8690,7 +8690,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260715_205054.xlsx
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
